--- a/Data/VedicSociety.xlsx
+++ b/Data/VedicSociety.xlsx
@@ -472,108 +472,108 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Who were ‘Nishadas’ as per Vedic references?</t>
+          <t>The Atharvaveda is primarily associated with:</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Sacrifice</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Enemies</t>
+          <t>War</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Forest dwellers</t>
+          <t>Medicine and spells</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Traders</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Forest dwellers</t>
+          <t>Medicine and spells</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which goddess is mentioned in Vedic texts as the goddess of speech?</t>
+          <t>Agni in Vedic literature is the god of:</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Durga</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Parvati</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lakshmi</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>‘Soma’ was a:</t>
+          <t>Which term referred to tribal kinship group in Vedic society?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sacrificial animal</t>
+          <t>Grama</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hallucinogenic drink</t>
+          <t>Jana</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Rashtra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sacred book</t>
+          <t>Desh</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hallucinogenic drink</t>
+          <t>Jana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -616,828 +616,828 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The four ‘Ashramas’ in Vedic life refer to:</t>
+          <t>‘Nasadiya Sukta’ in the Rigveda is associated with:</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Caste groups</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Life stages</t>
+          <t>War</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Religious texts</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sacrifices</t>
+          <t>Law</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Life stages</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>In Vedic rituals, the 'Ashvamedha' was a:</t>
+          <t>Which of the following is a later Vedic text?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fertility rite</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Horse sacrifice</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rain ceremony</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Funeral</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Horse sacrifice</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Later Vedic society saw the beginning of:</t>
+          <t>Women in early Vedic society had:</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nomadic culture</t>
+          <t>No rights</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Republics</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Urbanization</t>
+          <t>No property rights</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>No religious roles</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Vedic text ‘Shatapatha Brahmana’ is related to which Veda?</t>
+          <t>‘Brahmacharya’ refers to which stage of life in Vedic philosophy?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Retirement</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Celibate student</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Renunciation</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Celibate student</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The term 'Dharma' during Vedic age mainly meant:</t>
+          <t>The term 'Arya' in Vedic texts refers to:</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Religion</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rituals</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Moral duty</t>
+          <t>Cultural group</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Caste law</t>
+          <t>Caste</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Moral duty</t>
+          <t>Cultural group</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>In the Later Vedic period, the power of the king became:</t>
+          <t>‘Soma’ was a:</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Less significant</t>
+          <t>Sacrificial animal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ceremonial</t>
+          <t>Hallucinogenic drink</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Sacred book</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>Hallucinogenic drink</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Upanishads emphasize which philosophical idea?</t>
+          <t>Which term refers to the priestly scholar in the Vedic age?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Rathi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bhakti</t>
+          <t>Purohita</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yajna</t>
+          <t>Senani</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Polytheism</t>
+          <t>Gopa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Purohita</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Vedic people primarily lived in which region of India?</t>
+          <t>What is the subject matter of ‘Nirukta’, one of the Vedangas?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Deccan Plateau</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Indo-Gangetic plain</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Punjab and Haryana</t>
+          <t>Etymology</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eastern India</t>
+          <t>Chanting</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Punjab and Haryana</t>
+          <t>Etymology</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Who performed the religious rituals in Vedic times?</t>
+          <t>Which goddess is mentioned in Vedic texts as the goddess of speech?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kshatriyas</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Shudras</t>
+          <t>Durga</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brahmins</t>
+          <t>Parvati</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaishyas</t>
+          <t>Lakshmi</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Brahmins</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Vedic education system emphasized:</t>
+          <t>Which social institution became prominent during the Later Vedic period?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Warrior skills</t>
+          <t>Sati</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Practical training</t>
+          <t>Caste system</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spiritual and moral training</t>
+          <t>Joint family</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Political science</t>
+          <t>Temple worship</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Spiritual and moral training</t>
+          <t>Caste system</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The word ‘Aryavarta’ in Vedic literature refers to:</t>
+          <t>Who compiled the hymns of the Rigveda?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Southern India</t>
+          <t>Vashistha</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Entire Indian subcontinent</t>
+          <t>Vyasa</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Land of Aryans</t>
+          <t>Atri</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ganges delta</t>
+          <t>Patanjali</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Land of Aryans</t>
+          <t>Vyasa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What is the subject matter of ‘Nirukta’, one of the Vedangas?</t>
+          <t>Which text elaborates on the performance of Yajnas?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Brahmanas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Etymology</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chanting</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Etymology</t>
+          <t>Brahmanas</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which Vedic text contains the philosophical essence of the Vedas?</t>
+          <t>What was the role of 'Brahmins' in Vedic society?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brahmana</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aranyaka</t>
+          <t>Traders</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Priests and scholars</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smritis</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Priests and scholars</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which Vedic river is frequently mentioned in the Rigveda?</t>
+          <t>Which stage of life emphasized forest-dwelling and meditation?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Grihastha</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Brahmacharya</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Sannyasa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which of the following is considered a Vedanga?</t>
+          <t>What was the role of 'Vaishyas' in the Vedic period?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brahmana</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Aranyaka</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jyotisha</t>
+          <t>Agriculture and trade</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Upanishad</t>
+          <t>Slaves</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Jyotisha</t>
+          <t>Agriculture and trade</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which metal was known to the Vedic people?</t>
+          <t>Which of the following is considered a Vedanga?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Brahmana</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Aranyaka</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Jyotisha</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Alloys</t>
+          <t>Upanishad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Jyotisha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Who among the following composed hymns in the Rigveda?</t>
+          <t>Which was the language of Vedic literature?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vyasa</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Valmiki</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rishis</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rishis</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The term ‘Yajna’ in the Vedic period refers to:</t>
+          <t>Which Vedic text contains the philosophical essence of the Vedas?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Meditation</t>
+          <t>Brahmana</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Farming</t>
+          <t>Aranyaka</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sacrifice/ritual</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>War strategy</t>
+          <t>Smritis</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sacrifice/ritual</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Who among the following was a famous female seer (Rishika) in the Rigveda?</t>
+          <t>Who were known as ‘Rajanyas’ in Vedic texts?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lopamudra</t>
+          <t>Farmers</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Maitreyi</t>
+          <t>Warrior class</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gargi</t>
+          <t>Servants</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Warrior class</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The ‘Gayatri Mantra’ is found in which Veda?</t>
+          <t>‘Panis’ in the Rigveda were described as:</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Merchants</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Enemies or demons</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Cattle herders</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Enemies or demons</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The term 'Grihapati' in the Vedic society referred to:</t>
+          <t>In the Later Vedic period, the power of the king became:</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Village head</t>
+          <t>Less significant</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Ceremonial</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Head of the family</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Warrior</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Head of the family</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which of the following was not a social class in Vedic society?</t>
+          <t>The practice of ‘Sati’ is:</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brahmin</t>
+          <t>Mentioned in Rigveda</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Kshatriya</t>
+          <t>Later development</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sudra</t>
+          <t>Prescribed in Upanishads</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dalit</t>
+          <t>Practiced in Early Vedic period</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dalit</t>
+          <t>Later development</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The term ‘Rita’ in Vedic culture refers to:</t>
+          <t>Which metal was known to the Vedic people?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rituals</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sacrifice</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cosmic order</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wealth</t>
+          <t>Alloys</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cosmic order</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1480,1692 +1480,1692 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which term refers to the priestly scholar in the Vedic age?</t>
+          <t>The 'Purusha Sukta' of the Rigveda describes the origin of:</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rathi</t>
+          <t>The Universe</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Purohita</t>
+          <t>Castes</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Senani</t>
+          <t>Kingship</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gopa</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Purohita</t>
+          <t>Castes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which of the following is a later Vedic text?</t>
+          <t>The decline of the Rigvedic society was marked by:</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>End of tribal assemblies</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Rise of democratic rule</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Mass migration</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Urbanization</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>End of tribal assemblies</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>‘Panis’ in the Rigveda were described as:</t>
+          <t>Which of the following was not a social class in Vedic society?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Brahmin</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Merchants</t>
+          <t>Kshatriya</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Enemies or demons</t>
+          <t>Sudra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cattle herders</t>
+          <t>Dalit</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Enemies or demons</t>
+          <t>Dalit</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What is the primary source of knowledge about the early Vedic society?</t>
+          <t>The term 'Dharma' during Vedic age mainly meant:</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Manusmriti</t>
+          <t>Rituals</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vedas</t>
+          <t>Moral duty</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Caste law</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Vedas</t>
+          <t>Moral duty</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which social institution became prominent during the Later Vedic period?</t>
+          <t>The term ‘Yajna’ in the Vedic period refers to:</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sati</t>
+          <t>Meditation</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Caste system</t>
+          <t>Farming</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Joint family</t>
+          <t>Sacrifice/ritual</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Temple worship</t>
+          <t>War strategy</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Caste system</t>
+          <t>Sacrifice/ritual</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Atharvaveda is primarily associated with:</t>
+          <t>Who performed the religious rituals in Vedic times?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sacrifice</t>
+          <t>Kshatriyas</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Shudras</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medicine and spells</t>
+          <t>Brahmins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Vaishyas</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Medicine and spells</t>
+          <t>Brahmins</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>‘Gopati’ in the Vedic period means:</t>
+          <t>‘Varnashrama Dharma’ is a concept developed in which period?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Village leader</t>
+          <t>Early Vedic</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cow protector</t>
+          <t>Later Vedic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>God</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Scholar</t>
+          <t>Buddhist</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cow protector</t>
+          <t>Later Vedic</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which Vedic deity is associated with the Sun?</t>
+          <t>Which Vedic deity is associated with thunder and war?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Varuna</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Agni</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Indra</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Surya</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Agni</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Soma</t>
+          <t>Vayu</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Vedic economy was primarily:</t>
+          <t>‘Gopati’ in the Vedic period means:</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Village leader</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Agrarian</t>
+          <t>Cow protector</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>God</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trade-based</t>
+          <t>Scholar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Agrarian</t>
+          <t>Cow protector</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Women in early Vedic society had:</t>
+          <t>Who was responsible for protecting the tribe in Vedic society?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No rights</t>
+          <t>Brahmin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Vaishya</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>No property rights</t>
+          <t>King (Rajan)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>No religious roles</t>
+          <t>Guru</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>King (Rajan)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which Vedic god is considered as the messenger between gods and humans?</t>
+          <t>Which animal was the most sacred and central to Vedic rituals?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Goat</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>‘Vratyas’ in the Vedic period were:</t>
+          <t>Which Vedic deity is associated with the Sun?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Outcastes</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Nomadic tribes</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Scholars</t>
+          <t>Soma</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Outcastes</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>‘Dasas’ and ‘Dasyus’ referred to:</t>
+          <t>What is the primary source of knowledge about the early Vedic society?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Enemies</t>
+          <t>Manusmriti</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Craftsmen</t>
+          <t>Vedas</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slaves and indigenous people</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Slaves and indigenous people</t>
+          <t>Vedas</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which was the language of Vedic literature?</t>
+          <t>The Later Vedic society saw the emergence of:</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Tribal democracy</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Slavery</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Guilds</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which god was most important in the Rigvedic period?</t>
+          <t>The Upanishads emphasize which philosophical idea?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shiva</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Bhakti</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Yajna</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brahma</t>
+          <t>Polytheism</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>‘Brahmacharya’ refers to which stage of life in Vedic philosophy?</t>
+          <t>In the Later Vedic period, who performed the ‘Rajasuya’ sacrifice?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Traders</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Celibate student</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Renunciation</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Celibate student</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The practice of ‘Sati’ is:</t>
+          <t>What was the term used for tax or offering to the king?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mentioned in Rigveda</t>
+          <t>Dharma</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Later development</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Prescribed in Upanishads</t>
+          <t>Daan</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Practiced in Early Vedic period</t>
+          <t>Yajna</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Later development</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>‘Varnashrama Dharma’ is a concept developed in which period?</t>
+          <t>Which Vedic god was considered the ‘King of Gods’?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Early Vedic</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Later Vedic</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Buddhist</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Later Vedic</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Who were known as ‘Rajanyas’ in Vedic texts?</t>
+          <t>The education in Vedic times was imparted at:</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Farmers</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Warrior class</t>
+          <t>Gurukuls</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Servants</t>
+          <t>Palaces</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Monasteries</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Warrior class</t>
+          <t>Gurukuls</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which stage of life emphasized forest-dwelling and meditation?</t>
+          <t>In the Vedic age, 'Sabha' and 'Samiti' were:</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Grihastha</t>
+          <t>Religious texts</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Brahmacharya</t>
+          <t>Festivals</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Tribal assemblies</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sannyasa</t>
+          <t>Yajnas</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Tribal assemblies</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The social order in Vedic times was initially based on:</t>
+          <t>Who among the following was a famous female seer (Rishika) in the Rigveda?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Birth</t>
+          <t>Lopamudra</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Occupation</t>
+          <t>Maitreyi</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Gargi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Occupation</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The education in Vedic times was imparted at:</t>
+          <t>The four ‘Ashramas’ in Vedic life refer to:</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Caste groups</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Gurukuls</t>
+          <t>Life stages</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Palaces</t>
+          <t>Religious texts</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Monasteries</t>
+          <t>Sacrifices</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gurukuls</t>
+          <t>Life stages</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which term referred to tribal kinship group in Vedic society?</t>
+          <t>The Vedic people primarily lived in which region of India?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Grama</t>
+          <t>Deccan Plateau</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Jana</t>
+          <t>Indo-Gangetic plain</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rashtra</t>
+          <t>Punjab and Haryana</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Desh</t>
+          <t>Eastern India</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Jana</t>
+          <t>Punjab and Haryana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which stage followed Grihastha in the ashrama system?</t>
+          <t>Which Vedic river is frequently mentioned in the Rigveda?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brahmacharya</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sannyasa</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The decline of the Rigvedic society was marked by:</t>
+          <t>Which god was most important in the Rigvedic period?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>End of tribal assemblies</t>
+          <t>Shiva</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Rise of democratic rule</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mass migration</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Urbanization</t>
+          <t>Brahma</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>End of tribal assemblies</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The 'Purusha Sukta' of the Rigveda describes the origin of:</t>
+          <t>Which Vedic god is regarded as the sustainer of cosmic and moral order?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>The Universe</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Castes</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kingship</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Vayu</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Castes</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which text elaborates on the performance of Yajnas?</t>
+          <t>In Vedic rituals, the 'Ashvamedha' was a:</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Fertility rite</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Brahmanas</t>
+          <t>Horse sacrifice</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Rain ceremony</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Funeral</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Brahmanas</t>
+          <t>Horse sacrifice</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>In the Later Vedic period, who performed the ‘Rajasuya’ sacrifice?</t>
+          <t>‘Vratyas’ in the Vedic period were:</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Traders</t>
+          <t>Outcastes</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>Nomadic tribes</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>Warriors</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Kings</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Scholars</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Outcastes</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What was the role of 'Vaishyas' in the Vedic period?</t>
+          <t>In Vedic rituals, who recited hymns and performed sacrifices?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Shudras</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Vaishyas</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Agriculture and trade</t>
+          <t>Brahmins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Slaves</t>
+          <t>Rishis</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Agriculture and trade</t>
+          <t>Brahmins</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Later Vedic society saw the emergence of:</t>
+          <t>The Vedic text ‘Shatapatha Brahmana’ is related to which Veda?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tribal democracy</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Slavery</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guilds</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which animal was the most sacred and central to Vedic rituals?</t>
+          <t>The social order in Vedic times was initially based on:</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Birth</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Occupation</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Goat</t>
+          <t>Property</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Occupation</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Agni in Vedic literature is the god of:</t>
+          <t>The term ‘Rita’ in Vedic culture refers to:</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Rituals</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Sacrifice</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Cosmic order</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Wealth</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Cosmic order</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which Vedic god is regarded as the sustainer of cosmic and moral order?</t>
+          <t>‘Dasas’ and ‘Dasyus’ referred to:</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Enemies</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Craftsmen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vayu</t>
+          <t>Slaves and indigenous people</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Slaves and indigenous people</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Who was responsible for protecting the tribe in Vedic society?</t>
+          <t>The word ‘Aryavarta’ in Vedic literature refers to:</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brahmin</t>
+          <t>Southern India</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Vaishya</t>
+          <t>Entire Indian subcontinent</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>King (Rajan)</t>
+          <t>Land of Aryans</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Guru</t>
+          <t>Ganges delta</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>King (Rajan)</t>
+          <t>Land of Aryans</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which Vedic text primarily deals with melodies and chants?</t>
+          <t>Which stage followed Grihastha in the ashrama system?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Brahmacharya</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Sannyasa</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>‘Nasadiya Sukta’ in the Rigveda is associated with:</t>
+          <t>The ‘Gayatri Mantra’ is found in which Veda?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cosmology</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cosmology</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>In Vedic rituals, who recited hymns and performed sacrifices?</t>
+          <t>What marked the transition from Early to Later Vedic period?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Shudras</t>
+          <t>Discovery of fire</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Vaishyas</t>
+          <t>Geographical shift eastwards</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Brahmins</t>
+          <t>Introduction of Jainism</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rishis</t>
+          <t>Fall of Harappan cities</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Brahmins</t>
+          <t>Geographical shift eastwards</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The term 'Arya' in Vedic texts refers to:</t>
+          <t>The Later Vedic society saw the beginning of:</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Race</t>
+          <t>Nomadic culture</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Republics</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cultural group</t>
+          <t>Urbanization</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Caste</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cultural group</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What was the role of 'Brahmins' in Vedic society?</t>
+          <t>Which Vedic god is considered as the messenger between gods and humans?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Traders</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Priests and scholars</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Priests and scholars</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What was the main occupation of the Vedic Aryans?</t>
+          <t>Which Veda is considered the oldest?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hunting</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Craftsmanship</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which Vedic god was considered the ‘King of Gods’?</t>
+          <t>The term 'Grihapati' in the Vedic society referred to:</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Village head</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Head of the family</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Warrior</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Head of the family</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>In the Vedic age, 'Sabha' and 'Samiti' were:</t>
+          <t>Who among the following composed hymns in the Rigveda?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Religious texts</t>
+          <t>Vyasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Festivals</t>
+          <t>Valmiki</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Tribal assemblies</t>
+          <t>Rishis</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Yajnas</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tribal assemblies</t>
+          <t>Rishis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What was the term used for tax or offering to the king?</t>
+          <t>Which Vedic text primarily deals with melodies and chants?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dharma</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Daan</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Yajna</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What marked the transition from Early to Later Vedic period?</t>
+          <t>Who were ‘Nishadas’ as per Vedic references?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Discovery of fire</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Geographical shift eastwards</t>
+          <t>Enemies</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Introduction of Jainism</t>
+          <t>Forest dwellers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fall of Harappan cities</t>
+          <t>Traders</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Geographical shift eastwards</t>
+          <t>Forest dwellers</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which Veda is considered the oldest?</t>
+          <t>The Vedic education system emphasized:</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Warrior skills</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Practical training</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Spiritual and moral training</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Political science</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Spiritual and moral training</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Who compiled the hymns of the Rigveda?</t>
+          <t>The Vedic economy was primarily:</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Vashistha</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Vyasa</t>
+          <t>Agrarian</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Atri</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Patanjali</t>
+          <t>Trade-based</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Vyasa</t>
+          <t>Agrarian</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which Vedic deity is associated with thunder and war?</t>
+          <t>What was the main occupation of the Vedic Aryans?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Hunting</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vayu</t>
+          <t>Craftsmanship</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>

--- a/Data/VedicSociety.xlsx
+++ b/Data/VedicSociety.xlsx
@@ -472,16 +472,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Atharvaveda is primarily associated with:</t>
+          <t>‘Nasadiya Sukta’ in the Rigveda is associated with:</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sacrifice</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,53 +491,53 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Medicine and spells</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Law</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Medicine and spells</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Agni in Vedic literature is the god of:</t>
+          <t>The term ‘Yupa’ in Vedic rituals refers to:</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Sacred chant</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Sacrifice altar</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Pillar for tying the sacrificial animal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Priest robe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Pillar for tying the sacrificial animal</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -580,52 +580,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The term ‘Yupa’ in Vedic rituals refers to:</t>
+          <t>Agni in Vedic literature is the god of:</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sacred chant</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sacrifice altar</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pillar for tying the sacrificial animal</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Priest robe</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pillar for tying the sacrificial animal</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>‘Nasadiya Sukta’ in the Rigveda is associated with:</t>
+          <t>The Atharvaveda is primarily associated with:</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cosmology</t>
+          <t>Sacrifice</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -635,2537 +635,2537 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Medicine and spells</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Law</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cosmology</t>
+          <t>Medicine and spells</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which of the following is a later Vedic text?</t>
+          <t>Who compiled the hymns of the Rigveda?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Vashistha</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Vyasa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Atri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Patanjali</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Vyasa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Women in early Vedic society had:</t>
+          <t>Which social institution became prominent during the Later Vedic period?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No rights</t>
+          <t>Sati</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Caste system</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>No property rights</t>
+          <t>Joint family</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No religious roles</t>
+          <t>Temple worship</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Caste system</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>‘Brahmacharya’ refers to which stage of life in Vedic philosophy?</t>
+          <t>Which goddess is mentioned in Vedic texts as the goddess of speech?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Durga</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Celibate student</t>
+          <t>Parvati</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Renunciation</t>
+          <t>Lakshmi</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Celibate student</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The term 'Arya' in Vedic texts refers to:</t>
+          <t>What is the subject matter of ‘Nirukta’, one of the Vedangas?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Race</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cultural group</t>
+          <t>Etymology</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Caste</t>
+          <t>Chanting</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cultural group</t>
+          <t>Etymology</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>‘Soma’ was a:</t>
+          <t>Which term refers to the priestly scholar in the Vedic age?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sacrificial animal</t>
+          <t>Rathi</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hallucinogenic drink</t>
+          <t>Purohita</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Senani</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sacred book</t>
+          <t>Gopa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hallucinogenic drink</t>
+          <t>Purohita</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which term refers to the priestly scholar in the Vedic age?</t>
+          <t>‘Soma’ was a:</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rathi</t>
+          <t>Sacrificial animal</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Purohita</t>
+          <t>Hallucinogenic drink</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Senani</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gopa</t>
+          <t>Sacred book</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Purohita</t>
+          <t>Hallucinogenic drink</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What is the subject matter of ‘Nirukta’, one of the Vedangas?</t>
+          <t>The term 'Arya' in Vedic texts refers to:</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Etymology</t>
+          <t>Cultural group</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chanting</t>
+          <t>Caste</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Etymology</t>
+          <t>Cultural group</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which goddess is mentioned in Vedic texts as the goddess of speech?</t>
+          <t>‘Brahmacharya’ refers to which stage of life in Vedic philosophy?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Durga</t>
+          <t>Retirement</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Parvati</t>
+          <t>Celibate student</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lakshmi</t>
+          <t>Renunciation</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Celibate student</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which social institution became prominent during the Later Vedic period?</t>
+          <t>Women in early Vedic society had:</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sati</t>
+          <t>No rights</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Caste system</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Joint family</t>
+          <t>No property rights</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Temple worship</t>
+          <t>No religious roles</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Caste system</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Who compiled the hymns of the Rigveda?</t>
+          <t>Which of the following is a later Vedic text?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vashistha</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Vyasa</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atri</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Patanjali</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Vyasa</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which text elaborates on the performance of Yajnas?</t>
+          <t>In the Later Vedic period, the power of the king became:</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Less significant</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Brahmanas</t>
+          <t>Ceremonial</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Brahmanas</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What was the role of 'Brahmins' in Vedic society?</t>
+          <t>‘Panis’ in the Rigveda were described as:</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Traders</t>
+          <t>Merchants</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Priests and scholars</t>
+          <t>Enemies or demons</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Cattle herders</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Priests and scholars</t>
+          <t>Enemies or demons</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which stage of life emphasized forest-dwelling and meditation?</t>
+          <t>Who were known as ‘Rajanyas’ in Vedic texts?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Grihastha</t>
+          <t>Farmers</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Brahmacharya</t>
+          <t>Warrior class</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Servants</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sannyasa</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Warrior class</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What was the role of 'Vaishyas' in the Vedic period?</t>
+          <t>Which Vedic text contains the philosophical essence of the Vedas?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Brahmana</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Aranyaka</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Agriculture and trade</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slaves</t>
+          <t>Smritis</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Agriculture and trade</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which of the following is considered a Vedanga?</t>
+          <t>Which was the language of Vedic literature?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brahmana</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aranyaka</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jyotisha</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Upanishad</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Jyotisha</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which was the language of Vedic literature?</t>
+          <t>Which of the following is considered a Vedanga?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Brahmana</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Aranyaka</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Jyotisha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Upanishad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Jyotisha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which Vedic text contains the philosophical essence of the Vedas?</t>
+          <t>What was the role of 'Vaishyas' in the Vedic period?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brahmana</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Aranyaka</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Agriculture and trade</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smritis</t>
+          <t>Slaves</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Agriculture and trade</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Who were known as ‘Rajanyas’ in Vedic texts?</t>
+          <t>Which stage of life emphasized forest-dwelling and meditation?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Farmers</t>
+          <t>Grihastha</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Warrior class</t>
+          <t>Brahmacharya</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Servants</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Sannyasa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Warrior class</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>‘Panis’ in the Rigveda were described as:</t>
+          <t>What was the role of 'Brahmins' in Vedic society?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Merchants</t>
+          <t>Traders</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Enemies or demons</t>
+          <t>Priests and scholars</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cattle herders</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Enemies or demons</t>
+          <t>Priests and scholars</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>In the Later Vedic period, the power of the king became:</t>
+          <t>Which text elaborates on the performance of Yajnas?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Less significant</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ceremonial</t>
+          <t>Brahmanas</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>Brahmanas</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The practice of ‘Sati’ is:</t>
+          <t>‘Varnashrama Dharma’ is a concept developed in which period?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mentioned in Rigveda</t>
+          <t>Early Vedic</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Later development</t>
+          <t>Later Vedic</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Prescribed in Upanishads</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Practiced in Early Vedic period</t>
+          <t>Buddhist</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Later development</t>
+          <t>Later Vedic</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which metal was known to the Vedic people?</t>
+          <t>Who performed the religious rituals in Vedic times?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Kshatriyas</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Shudras</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Brahmins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alloys</t>
+          <t>Vaishyas</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Brahmins</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The term ‘Nadi’ in Rigveda refers to:</t>
+          <t>The term ‘Yajna’ in the Vedic period refers to:</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Meditation</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Farming</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Sacrifice/ritual</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>War strategy</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Sacrifice/ritual</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The 'Purusha Sukta' of the Rigveda describes the origin of:</t>
+          <t>The term 'Dharma' during Vedic age mainly meant:</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>The Universe</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Castes</t>
+          <t>Rituals</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kingship</t>
+          <t>Moral duty</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Caste law</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Castes</t>
+          <t>Moral duty</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The decline of the Rigvedic society was marked by:</t>
+          <t>Which of the following was not a social class in Vedic society?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>End of tribal assemblies</t>
+          <t>Brahmin</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rise of democratic rule</t>
+          <t>Kshatriya</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mass migration</t>
+          <t>Sudra</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Urbanization</t>
+          <t>Dalit</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>End of tribal assemblies</t>
+          <t>Dalit</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which of the following was not a social class in Vedic society?</t>
+          <t>The decline of the Rigvedic society was marked by:</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brahmin</t>
+          <t>End of tribal assemblies</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Kshatriya</t>
+          <t>Rise of democratic rule</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sudra</t>
+          <t>Mass migration</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dalit</t>
+          <t>Urbanization</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dalit</t>
+          <t>End of tribal assemblies</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The term 'Dharma' during Vedic age mainly meant:</t>
+          <t>The 'Purusha Sukta' of the Rigveda describes the origin of:</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Religion</t>
+          <t>The Universe</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Rituals</t>
+          <t>Castes</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Moral duty</t>
+          <t>Kingship</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Caste law</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Moral duty</t>
+          <t>Castes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The term ‘Yajna’ in the Vedic period refers to:</t>
+          <t>The term ‘Nadi’ in Rigveda refers to:</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Meditation</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Farming</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sacrifice/ritual</t>
+          <t>River</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>War strategy</t>
+          <t>Mountain</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sacrifice/ritual</t>
+          <t>River</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Who performed the religious rituals in Vedic times?</t>
+          <t>Which metal was known to the Vedic people?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kshatriyas</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Shudras</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Brahmins</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vaishyas</t>
+          <t>Alloys</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Brahmins</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>‘Varnashrama Dharma’ is a concept developed in which period?</t>
+          <t>The practice of ‘Sati’ is:</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Early Vedic</t>
+          <t>Mentioned in Rigveda</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Later Vedic</t>
+          <t>Later development</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Prescribed in Upanishads</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Buddhist</t>
+          <t>Practiced in Early Vedic period</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Later Vedic</t>
+          <t>Later development</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which Vedic deity is associated with thunder and war?</t>
+          <t>What was the term used for tax or offering to the king?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Dharma</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Daan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vayu</t>
+          <t>Yajna</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>‘Gopati’ in the Vedic period means:</t>
+          <t>In the Later Vedic period, who performed the ‘Rajasuya’ sacrifice?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Village leader</t>
+          <t>Traders</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cow protector</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>God</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Scholar</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cow protector</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Who was responsible for protecting the tribe in Vedic society?</t>
+          <t>The Upanishads emphasize which philosophical idea?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brahmin</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Vaishya</t>
+          <t>Bhakti</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>King (Rajan)</t>
+          <t>Yajna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guru</t>
+          <t>Polytheism</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>King (Rajan)</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which animal was the most sacred and central to Vedic rituals?</t>
+          <t>The Later Vedic society saw the emergence of:</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Tribal democracy</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Slavery</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Goat</t>
+          <t>Guilds</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which Vedic deity is associated with the Sun?</t>
+          <t>What is the primary source of knowledge about the early Vedic society?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Manusmriti</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Vedas</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Soma</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Vedas</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What is the primary source of knowledge about the early Vedic society?</t>
+          <t>Which Vedic deity is associated with the Sun?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Manusmriti</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vedas</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Soma</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Vedas</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Later Vedic society saw the emergence of:</t>
+          <t>Which animal was the most sacred and central to Vedic rituals?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tribal democracy</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Slavery</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guilds</t>
+          <t>Goat</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Upanishads emphasize which philosophical idea?</t>
+          <t>Who was responsible for protecting the tribe in Vedic society?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Brahmin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Bhakti</t>
+          <t>Vaishya</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Yajna</t>
+          <t>King (Rajan)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Polytheism</t>
+          <t>Guru</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>King (Rajan)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>In the Later Vedic period, who performed the ‘Rajasuya’ sacrifice?</t>
+          <t>‘Gopati’ in the Vedic period means:</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Traders</t>
+          <t>Village leader</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Cow protector</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>God</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Scholar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Cow protector</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What was the term used for tax or offering to the king?</t>
+          <t>Which Vedic deity is associated with thunder and war?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dharma</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Daan</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yajna</t>
+          <t>Vayu</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which Vedic god was considered the ‘King of Gods’?</t>
+          <t>In Vedic rituals, the 'Ashvamedha' was a:</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Fertility rite</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Horse sacrifice</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Rain ceremony</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Funeral</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Horse sacrifice</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The education in Vedic times was imparted at:</t>
+          <t>Which Vedic god is regarded as the sustainer of cosmic and moral order?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Gurukuls</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Palaces</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Monasteries</t>
+          <t>Vayu</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gurukuls</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>In the Vedic age, 'Sabha' and 'Samiti' were:</t>
+          <t>Which god was most important in the Rigvedic period?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Religious texts</t>
+          <t>Shiva</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Festivals</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tribal assemblies</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Yajnas</t>
+          <t>Brahma</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tribal assemblies</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who among the following was a famous female seer (Rishika) in the Rigveda?</t>
+          <t>Which Vedic river is frequently mentioned in the Rigveda?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lopamudra</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Maitreyi</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gargi</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The four ‘Ashramas’ in Vedic life refer to:</t>
+          <t>The Vedic people primarily lived in which region of India?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Caste groups</t>
+          <t>Deccan Plateau</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Life stages</t>
+          <t>Indo-Gangetic plain</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Religious texts</t>
+          <t>Punjab and Haryana</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sacrifices</t>
+          <t>Eastern India</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Life stages</t>
+          <t>Punjab and Haryana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Vedic people primarily lived in which region of India?</t>
+          <t>The four ‘Ashramas’ in Vedic life refer to:</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Deccan Plateau</t>
+          <t>Caste groups</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Indo-Gangetic plain</t>
+          <t>Life stages</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Punjab and Haryana</t>
+          <t>Religious texts</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Eastern India</t>
+          <t>Sacrifices</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Punjab and Haryana</t>
+          <t>Life stages</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which Vedic river is frequently mentioned in the Rigveda?</t>
+          <t>Who among the following was a famous female seer (Rishika) in the Rigveda?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Lopamudra</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Maitreyi</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Gargi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which god was most important in the Rigvedic period?</t>
+          <t>In the Vedic age, 'Sabha' and 'Samiti' were:</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Shiva</t>
+          <t>Religious texts</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Festivals</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Tribal assemblies</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brahma</t>
+          <t>Yajnas</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Tribal assemblies</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which Vedic god is regarded as the sustainer of cosmic and moral order?</t>
+          <t>The education in Vedic times was imparted at:</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Gurukuls</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Palaces</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vayu</t>
+          <t>Monasteries</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Gurukuls</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>In Vedic rituals, the 'Ashvamedha' was a:</t>
+          <t>Which Vedic god was considered the ‘King of Gods’?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fertility rite</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Horse sacrifice</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rain ceremony</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Funeral</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Horse sacrifice</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>‘Vratyas’ in the Vedic period were:</t>
+          <t>What marked the transition from Early to Later Vedic period?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Outcastes</t>
+          <t>Discovery of fire</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Nomadic tribes</t>
+          <t>Geographical shift eastwards</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Introduction of Jainism</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Scholars</t>
+          <t>Fall of Harappan cities</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Outcastes</t>
+          <t>Geographical shift eastwards</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>In Vedic rituals, who recited hymns and performed sacrifices?</t>
+          <t>The ‘Gayatri Mantra’ is found in which Veda?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Shudras</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Vaishyas</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Brahmins</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rishis</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Brahmins</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Vedic text ‘Shatapatha Brahmana’ is related to which Veda?</t>
+          <t>Which stage followed Grihastha in the ashrama system?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Brahmacharya</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Sannyasa</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The social order in Vedic times was initially based on:</t>
+          <t>The word ‘Aryavarta’ in Vedic literature refers to:</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Birth</t>
+          <t>Southern India</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Occupation</t>
+          <t>Entire Indian subcontinent</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Land of Aryans</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>Ganges delta</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Occupation</t>
+          <t>Land of Aryans</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The term ‘Rita’ in Vedic culture refers to:</t>
+          <t>‘Dasas’ and ‘Dasyus’ referred to:</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rituals</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sacrifice</t>
+          <t>Enemies</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cosmic order</t>
+          <t>Craftsmen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wealth</t>
+          <t>Slaves and indigenous people</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cosmic order</t>
+          <t>Slaves and indigenous people</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>‘Dasas’ and ‘Dasyus’ referred to:</t>
+          <t>The term ‘Rita’ in Vedic culture refers to:</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Rituals</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Enemies</t>
+          <t>Sacrifice</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Craftsmen</t>
+          <t>Cosmic order</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Slaves and indigenous people</t>
+          <t>Wealth</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Slaves and indigenous people</t>
+          <t>Cosmic order</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The word ‘Aryavarta’ in Vedic literature refers to:</t>
+          <t>The social order in Vedic times was initially based on:</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Southern India</t>
+          <t>Birth</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Entire Indian subcontinent</t>
+          <t>Occupation</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Land of Aryans</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ganges delta</t>
+          <t>Property</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Land of Aryans</t>
+          <t>Occupation</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which stage followed Grihastha in the ashrama system?</t>
+          <t>The Vedic text ‘Shatapatha Brahmana’ is related to which Veda?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brahmacharya</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sannyasa</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The ‘Gayatri Mantra’ is found in which Veda?</t>
+          <t>In Vedic rituals, who recited hymns and performed sacrifices?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Shudras</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Vaishyas</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Brahmins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Rishis</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Brahmins</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>What marked the transition from Early to Later Vedic period?</t>
+          <t>‘Vratyas’ in the Vedic period were:</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Discovery of fire</t>
+          <t>Outcastes</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Geographical shift eastwards</t>
+          <t>Nomadic tribes</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Introduction of Jainism</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fall of Harappan cities</t>
+          <t>Scholars</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Geographical shift eastwards</t>
+          <t>Outcastes</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Later Vedic society saw the beginning of:</t>
+          <t>What was the main occupation of the Vedic Aryans?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nomadic culture</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Republics</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Urbanization</t>
+          <t>Hunting</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Craftsmanship</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which Vedic god is considered as the messenger between gods and humans?</t>
+          <t>The Vedic economy was primarily:</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Agrarian</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Trade-based</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Agrarian</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which Veda is considered the oldest?</t>
+          <t>The Vedic education system emphasized:</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Warrior skills</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Practical training</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Spiritual and moral training</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Political science</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Spiritual and moral training</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The term 'Grihapati' in the Vedic society referred to:</t>
+          <t>Who were ‘Nishadas’ as per Vedic references?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Village head</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Enemies</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Head of the family</t>
+          <t>Forest dwellers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Warrior</t>
+          <t>Traders</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Head of the family</t>
+          <t>Forest dwellers</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Who among the following composed hymns in the Rigveda?</t>
+          <t>Which Vedic text primarily deals with melodies and chants?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Vyasa</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Valmiki</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rishis</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rishis</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which Vedic text primarily deals with melodies and chants?</t>
+          <t>Who among the following composed hymns in the Rigveda?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Vyasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Valmiki</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Rishis</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Rishis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Who were ‘Nishadas’ as per Vedic references?</t>
+          <t>The term 'Grihapati' in the Vedic society referred to:</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Village head</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Enemies</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Forest dwellers</t>
+          <t>Head of the family</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Traders</t>
+          <t>Warrior</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Forest dwellers</t>
+          <t>Head of the family</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Vedic education system emphasized:</t>
+          <t>Which Veda is considered the oldest?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Warrior skills</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Practical training</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Spiritual and moral training</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Political science</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Spiritual and moral training</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Vedic economy was primarily:</t>
+          <t>Which Vedic god is considered as the messenger between gods and humans?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Agrarian</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trade-based</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Agrarian</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What was the main occupation of the Vedic Aryans?</t>
+          <t>The Later Vedic society saw the beginning of:</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Nomadic culture</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Republics</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hunting</t>
+          <t>Urbanization</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Craftsmanship</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>

--- a/Data/VedicSociety.xlsx
+++ b/Data/VedicSociety.xlsx
@@ -472,216 +472,216 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>‘Nasadiya Sukta’ in the Rigveda is associated with:</t>
+          <t>Which god was most important in the Rigvedic period?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cosmology</t>
+          <t>Shiva</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>Brahma</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cosmology</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The term ‘Yupa’ in Vedic rituals refers to:</t>
+          <t>‘Vratyas’ in the Vedic period were:</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sacred chant</t>
+          <t>Outcastes</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sacrifice altar</t>
+          <t>Nomadic tribes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pillar for tying the sacrificial animal</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Priest robe</t>
+          <t>Scholars</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pillar for tying the sacrificial animal</t>
+          <t>Outcastes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which term referred to tribal kinship group in Vedic society?</t>
+          <t>Who among the following composed hymns in the Rigveda?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Grama</t>
+          <t>Vyasa</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jana</t>
+          <t>Valmiki</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rashtra</t>
+          <t>Rishis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Desh</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jana</t>
+          <t>Rishis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agni in Vedic literature is the god of:</t>
+          <t>Who among the following was a famous female seer (Rishika) in the Rigveda?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Lopamudra</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Maitreyi</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Gargi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Atharvaveda is primarily associated with:</t>
+          <t>The four ‘Ashramas’ in Vedic life refer to:</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sacrifice</t>
+          <t>Caste groups</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Life stages</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Medicine and spells</t>
+          <t>Religious texts</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Sacrifices</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Medicine and spells</t>
+          <t>Life stages</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who compiled the hymns of the Rigveda?</t>
+          <t>‘Dasas’ and ‘Dasyus’ referred to:</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vashistha</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vyasa</t>
+          <t>Enemies</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atri</t>
+          <t>Craftsmen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Patanjali</t>
+          <t>Slaves and indigenous people</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Vyasa</t>
+          <t>Slaves and indigenous people</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -724,705 +724,705 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which goddess is mentioned in Vedic texts as the goddess of speech?</t>
+          <t>The practice of ‘Sati’ is:</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Mentioned in Rigveda</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Durga</t>
+          <t>Later development</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Parvati</t>
+          <t>Prescribed in Upanishads</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lakshmi</t>
+          <t>Practiced in Early Vedic period</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Later development</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What is the subject matter of ‘Nirukta’, one of the Vedangas?</t>
+          <t>The term 'Dharma' during Vedic age mainly meant:</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Rituals</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Etymology</t>
+          <t>Moral duty</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chanting</t>
+          <t>Caste law</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Etymology</t>
+          <t>Moral duty</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which term refers to the priestly scholar in the Vedic age?</t>
+          <t>The Upanishads emphasize which philosophical idea?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rathi</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Purohita</t>
+          <t>Bhakti</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Senani</t>
+          <t>Yajna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gopa</t>
+          <t>Polytheism</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Purohita</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>‘Soma’ was a:</t>
+          <t>‘Gopati’ in the Vedic period means:</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sacrificial animal</t>
+          <t>Village leader</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hallucinogenic drink</t>
+          <t>Cow protector</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>God</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sacred book</t>
+          <t>Scholar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hallucinogenic drink</t>
+          <t>Cow protector</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The term 'Arya' in Vedic texts refers to:</t>
+          <t>What marked the transition from Early to Later Vedic period?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Race</t>
+          <t>Discovery of fire</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Geographical shift eastwards</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cultural group</t>
+          <t>Introduction of Jainism</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Caste</t>
+          <t>Fall of Harappan cities</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cultural group</t>
+          <t>Geographical shift eastwards</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>‘Brahmacharya’ refers to which stage of life in Vedic philosophy?</t>
+          <t>The term ‘Yajna’ in the Vedic period refers to:</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Meditation</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Farming</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Celibate student</t>
+          <t>Sacrifice/ritual</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Renunciation</t>
+          <t>War strategy</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Celibate student</t>
+          <t>Sacrifice/ritual</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Women in early Vedic society had:</t>
+          <t>‘Varnashrama Dharma’ is a concept developed in which period?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No rights</t>
+          <t>Early Vedic</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Later Vedic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>No property rights</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>No religious roles</t>
+          <t>Buddhist</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Later Vedic</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which of the following is a later Vedic text?</t>
+          <t>Which Veda is considered the oldest?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Yajurveda</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Atharvaveda</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Rigveda</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Samaveda</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Yajurveda</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Atharvaveda</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>In the Later Vedic period, the power of the king became:</t>
+          <t>The 'Purusha Sukta' of the Rigveda describes the origin of:</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Less significant</t>
+          <t>The Universe</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ceremonial</t>
+          <t>Castes</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>Kingship</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>Castes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>‘Panis’ in the Rigveda were described as:</t>
+          <t>In the Later Vedic period, who performed the ‘Rajasuya’ sacrifice?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Traders</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Warriors</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Kings</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Priests</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Merchants</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Enemies or demons</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Cattle herders</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Enemies or demons</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Who were known as ‘Rajanyas’ in Vedic texts?</t>
+          <t>In the Vedic age, 'Sabha' and 'Samiti' were:</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Farmers</t>
+          <t>Religious texts</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Warrior class</t>
+          <t>Festivals</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Servants</t>
+          <t>Tribal assemblies</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Yajnas</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Warrior class</t>
+          <t>Tribal assemblies</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which Vedic text contains the philosophical essence of the Vedas?</t>
+          <t>What is the subject matter of ‘Nirukta’, one of the Vedangas?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brahmana</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Aranyaka</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Etymology</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smritis</t>
+          <t>Chanting</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Etymology</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which was the language of Vedic literature?</t>
+          <t>‘Soma’ was a:</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Sacrificial animal</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Hallucinogenic drink</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Sacred book</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Hallucinogenic drink</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which of the following is considered a Vedanga?</t>
+          <t>Which term refers to the priestly scholar in the Vedic age?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brahmana</t>
+          <t>Rathi</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Aranyaka</t>
+          <t>Purohita</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jyotisha</t>
+          <t>Senani</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Upanishad</t>
+          <t>Gopa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Jyotisha</t>
+          <t>Purohita</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What was the role of 'Vaishyas' in the Vedic period?</t>
+          <t>Who was responsible for protecting the tribe in Vedic society?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Brahmin</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Vaishya</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Agriculture and trade</t>
+          <t>King (Rajan)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slaves</t>
+          <t>Guru</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Agriculture and trade</t>
+          <t>King (Rajan)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which stage of life emphasized forest-dwelling and meditation?</t>
+          <t>The Vedic education system emphasized:</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Grihastha</t>
+          <t>Warrior skills</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Brahmacharya</t>
+          <t>Practical training</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Spiritual and moral training</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sannyasa</t>
+          <t>Political science</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Spiritual and moral training</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What was the role of 'Brahmins' in Vedic society?</t>
+          <t>Which Vedic text primarily deals with melodies and chants?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Traders</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Priests and scholars</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Priests and scholars</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which text elaborates on the performance of Yajnas?</t>
+          <t>The education in Vedic times was imparted at:</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Brahmanas</t>
+          <t>Gurukuls</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Palaces</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Monasteries</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Brahmanas</t>
+          <t>Gurukuls</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>‘Varnashrama Dharma’ is a concept developed in which period?</t>
+          <t>Who compiled the hymns of the Rigveda?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Early Vedic</t>
+          <t>Vashistha</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Later Vedic</t>
+          <t>Vyasa</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Atri</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Buddhist</t>
+          <t>Patanjali</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Later Vedic</t>
+          <t>Vyasa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Who performed the religious rituals in Vedic times?</t>
+          <t>In Vedic rituals, who recited hymns and performed sacrifices?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kshatriyas</t>
+          <t>Shudras</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Shudras</t>
+          <t>Vaishyas</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaishyas</t>
+          <t>Rishis</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1444,1728 +1444,1728 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The term ‘Yajna’ in the Vedic period refers to:</t>
+          <t>Who were ‘Nishadas’ as per Vedic references?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Meditation</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Farming</t>
+          <t>Enemies</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sacrifice/ritual</t>
+          <t>Forest dwellers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>War strategy</t>
+          <t>Traders</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sacrifice/ritual</t>
+          <t>Forest dwellers</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The term 'Dharma' during Vedic age mainly meant:</t>
+          <t>The Vedic text ‘Shatapatha Brahmana’ is related to which Veda?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Religion</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Rituals</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Moral duty</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Caste law</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Moral duty</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which of the following was not a social class in Vedic society?</t>
+          <t>In Vedic rituals, the 'Ashvamedha' was a:</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brahmin</t>
+          <t>Fertility rite</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Kshatriya</t>
+          <t>Horse sacrifice</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sudra</t>
+          <t>Rain ceremony</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dalit</t>
+          <t>Funeral</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dalit</t>
+          <t>Horse sacrifice</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The decline of the Rigvedic society was marked by:</t>
+          <t>Which stage of life emphasized forest-dwelling and meditation?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>End of tribal assemblies</t>
+          <t>Grihastha</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Rise of democratic rule</t>
+          <t>Brahmacharya</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mass migration</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Urbanization</t>
+          <t>Sannyasa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>End of tribal assemblies</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The 'Purusha Sukta' of the Rigveda describes the origin of:</t>
+          <t>Which Vedic god is regarded as the sustainer of cosmic and moral order?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>The Universe</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Castes</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kingship</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Vayu</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Castes</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The term ‘Nadi’ in Rigveda refers to:</t>
+          <t>Who were known as ‘Rajanyas’ in Vedic texts?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Farmers</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Warrior class</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Servants</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Warrior class</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which metal was known to the Vedic people?</t>
+          <t>Which of the following is a later Vedic text?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Alloys</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The practice of ‘Sati’ is:</t>
+          <t>Which text elaborates on the performance of Yajnas?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mentioned in Rigveda</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Later development</t>
+          <t>Brahmanas</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Prescribed in Upanishads</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Practiced in Early Vedic period</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Later development</t>
+          <t>Brahmanas</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>What was the term used for tax or offering to the king?</t>
+          <t>Which Vedic deity is associated with the Sun?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dharma</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Daan</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Yajna</t>
+          <t>Soma</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>In the Later Vedic period, who performed the ‘Rajasuya’ sacrifice?</t>
+          <t>What was the main occupation of the Vedic Aryans?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Traders</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Hunting</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Craftsmanship</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Upanishads emphasize which philosophical idea?</t>
+          <t>The Vedic people primarily lived in which region of India?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Deccan Plateau</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Bhakti</t>
+          <t>Indo-Gangetic plain</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Yajna</t>
+          <t>Punjab and Haryana</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Polytheism</t>
+          <t>Eastern India</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Punjab and Haryana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Later Vedic society saw the emergence of:</t>
+          <t>The term 'Grihapati' in the Vedic society referred to:</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tribal democracy</t>
+          <t>Village head</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Slavery</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Head of the family</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guilds</t>
+          <t>Warrior</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Head of the family</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What is the primary source of knowledge about the early Vedic society?</t>
+          <t>Which Vedic god is considered as the messenger between gods and humans?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Manusmriti</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vedas</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Vedas</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which Vedic deity is associated with the Sun?</t>
+          <t>Which Vedic river is frequently mentioned in the Rigveda?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Soma</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which animal was the most sacred and central to Vedic rituals?</t>
+          <t>What is the primary source of knowledge about the early Vedic society?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Manusmriti</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Vedas</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Goat</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Vedas</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Who was responsible for protecting the tribe in Vedic society?</t>
+          <t>Which Vedic text contains the philosophical essence of the Vedas?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brahmin</t>
+          <t>Brahmana</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Vaishya</t>
+          <t>Aranyaka</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>King (Rajan)</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guru</t>
+          <t>Smritis</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>King (Rajan)</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>‘Gopati’ in the Vedic period means:</t>
+          <t>‘Panis’ in the Rigveda were described as:</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Village leader</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cow protector</t>
+          <t>Merchants</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>God</t>
+          <t>Enemies or demons</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Scholar</t>
+          <t>Cattle herders</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cow protector</t>
+          <t>Enemies or demons</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which Vedic deity is associated with thunder and war?</t>
+          <t>The term ‘Nadi’ in Rigveda refers to:</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>River</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vayu</t>
+          <t>Mountain</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>River</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>In Vedic rituals, the 'Ashvamedha' was a:</t>
+          <t>The term ‘Rita’ in Vedic culture refers to:</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fertility rite</t>
+          <t>Rituals</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Horse sacrifice</t>
+          <t>Sacrifice</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rain ceremony</t>
+          <t>Cosmic order</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Funeral</t>
+          <t>Wealth</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Horse sacrifice</t>
+          <t>Cosmic order</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which Vedic god is regarded as the sustainer of cosmic and moral order?</t>
+          <t>The word ‘Aryavarta’ in Vedic literature refers to:</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Southern India</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Entire Indian subcontinent</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Land of Aryans</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vayu</t>
+          <t>Ganges delta</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Land of Aryans</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which god was most important in the Rigvedic period?</t>
+          <t>Which term referred to tribal kinship group in Vedic society?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Shiva</t>
+          <t>Grama</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Jana</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Rashtra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brahma</t>
+          <t>Desh</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Jana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which Vedic river is frequently mentioned in the Rigveda?</t>
+          <t>The social order in Vedic times was initially based on:</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Birth</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Occupation</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Property</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Occupation</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Vedic people primarily lived in which region of India?</t>
+          <t>Which of the following is considered a Vedanga?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Deccan Plateau</t>
+          <t>Brahmana</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Indo-Gangetic plain</t>
+          <t>Aranyaka</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Punjab and Haryana</t>
+          <t>Jyotisha</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Eastern India</t>
+          <t>Upanishad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Punjab and Haryana</t>
+          <t>Jyotisha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The four ‘Ashramas’ in Vedic life refer to:</t>
+          <t>Who performed the religious rituals in Vedic times?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Caste groups</t>
+          <t>Kshatriyas</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Life stages</t>
+          <t>Shudras</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Religious texts</t>
+          <t>Brahmins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sacrifices</t>
+          <t>Vaishyas</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Life stages</t>
+          <t>Brahmins</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Who among the following was a famous female seer (Rishika) in the Rigveda?</t>
+          <t>Which of the following was not a social class in Vedic society?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lopamudra</t>
+          <t>Brahmin</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Maitreyi</t>
+          <t>Kshatriya</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gargi</t>
+          <t>Sudra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Dalit</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Dalit</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>In the Vedic age, 'Sabha' and 'Samiti' were:</t>
+          <t>Which Vedic god was considered the ‘King of Gods’?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Religious texts</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Festivals</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tribal assemblies</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Yajnas</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tribal assemblies</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The education in Vedic times was imparted at:</t>
+          <t>The Later Vedic society saw the emergence of:</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Tribal democracy</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Gurukuls</t>
+          <t>Slavery</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Palaces</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Monasteries</t>
+          <t>Guilds</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gurukuls</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which Vedic god was considered the ‘King of Gods’?</t>
+          <t>The Vedic economy was primarily:</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Agrarian</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Trade-based</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Agrarian</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What marked the transition from Early to Later Vedic period?</t>
+          <t>Which metal was known to the Vedic people?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Discovery of fire</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Geographical shift eastwards</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Introduction of Jainism</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fall of Harappan cities</t>
+          <t>Alloys</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Geographical shift eastwards</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The ‘Gayatri Mantra’ is found in which Veda?</t>
+          <t>Agni in Vedic literature is the god of:</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which stage followed Grihastha in the ashrama system?</t>
+          <t>What was the role of 'Vaishyas' in the Vedic period?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brahmacharya</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sannyasa</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Agriculture and trade</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Slaves</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Agriculture and trade</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The word ‘Aryavarta’ in Vedic literature refers to:</t>
+          <t>The Later Vedic society saw the beginning of:</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Southern India</t>
+          <t>Nomadic culture</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Entire Indian subcontinent</t>
+          <t>Republics</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Land of Aryans</t>
+          <t>Urbanization</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ganges delta</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Land of Aryans</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>‘Dasas’ and ‘Dasyus’ referred to:</t>
+          <t>The decline of the Rigvedic society was marked by:</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>End of tribal assemblies</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Enemies</t>
+          <t>Rise of democratic rule</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Craftsmen</t>
+          <t>Mass migration</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Slaves and indigenous people</t>
+          <t>Urbanization</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Slaves and indigenous people</t>
+          <t>End of tribal assemblies</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The term ‘Rita’ in Vedic culture refers to:</t>
+          <t>Which Vedic deity is associated with thunder and war?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rituals</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sacrifice</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cosmic order</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wealth</t>
+          <t>Vayu</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cosmic order</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The social order in Vedic times was initially based on:</t>
+          <t>What was the role of 'Brahmins' in Vedic society?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Birth</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Occupation</t>
+          <t>Traders</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Priests and scholars</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Occupation</t>
+          <t>Priests and scholars</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Vedic text ‘Shatapatha Brahmana’ is related to which Veda?</t>
+          <t>The term ‘Yupa’ in Vedic rituals refers to:</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Sacred chant</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Sacrifice altar</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Pillar for tying the sacrificial animal</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Priest robe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Pillar for tying the sacrificial animal</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>In Vedic rituals, who recited hymns and performed sacrifices?</t>
+          <t>‘Nasadiya Sukta’ in the Rigveda is associated with:</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Shudras</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Vaishyas</t>
+          <t>War</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Brahmins</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rishis</t>
+          <t>Law</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Brahmins</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>‘Vratyas’ in the Vedic period were:</t>
+          <t>Which animal was the most sacred and central to Vedic rituals?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Outcastes</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Nomadic tribes</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Scholars</t>
+          <t>Goat</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Outcastes</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>What was the main occupation of the Vedic Aryans?</t>
+          <t>Which was the language of Vedic literature?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hunting</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Craftsmanship</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Vedic economy was primarily:</t>
+          <t>In the Later Vedic period, the power of the king became:</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Less significant</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Agrarian</t>
+          <t>Ceremonial</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trade-based</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Agrarian</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Vedic education system emphasized:</t>
+          <t>Women in early Vedic society had:</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Warrior skills</t>
+          <t>No rights</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Practical training</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Spiritual and moral training</t>
+          <t>No property rights</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Political science</t>
+          <t>No religious roles</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Spiritual and moral training</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Who were ‘Nishadas’ as per Vedic references?</t>
+          <t>Which goddess is mentioned in Vedic texts as the goddess of speech?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Enemies</t>
+          <t>Durga</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Forest dwellers</t>
+          <t>Parvati</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Traders</t>
+          <t>Lakshmi</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Forest dwellers</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which Vedic text primarily deals with melodies and chants?</t>
+          <t>The term 'Arya' in Vedic texts refers to:</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Cultural group</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Caste</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Cultural group</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Who among the following composed hymns in the Rigveda?</t>
+          <t>The Atharvaveda is primarily associated with:</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Vyasa</t>
+          <t>Sacrifice</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Valmiki</t>
+          <t>War</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rishis</t>
+          <t>Medicine and spells</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rishis</t>
+          <t>Medicine and spells</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The term 'Grihapati' in the Vedic society referred to:</t>
+          <t>What was the term used for tax or offering to the king?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Village head</t>
+          <t>Dharma</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Head of the family</t>
+          <t>Daan</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Warrior</t>
+          <t>Yajna</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Head of the family</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which Veda is considered the oldest?</t>
+          <t>‘Brahmacharya’ refers to which stage of life in Vedic philosophy?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Retirement</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Celibate student</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Renunciation</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Celibate student</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which Vedic god is considered as the messenger between gods and humans?</t>
+          <t>Which stage followed Grihastha in the ashrama system?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Brahmacharya</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Sannyasa</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Later Vedic society saw the beginning of:</t>
+          <t>The ‘Gayatri Mantra’ is found in which Veda?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nomadic culture</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Republics</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Urbanization</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>

--- a/Data/VedicSociety.xlsx
+++ b/Data/VedicSociety.xlsx
@@ -472,1595 +472,1595 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which god was most important in the Rigvedic period?</t>
+          <t>Which stage of life emphasized forest-dwelling and meditation?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shiva</t>
+          <t>Grihastha</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Brahmacharya</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brahma</t>
+          <t>Sannyasa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>‘Vratyas’ in the Vedic period were:</t>
+          <t>What was the term used for tax or offering to the king?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Outcastes</t>
+          <t>Dharma</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nomadic tribes</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Daan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Scholars</t>
+          <t>Yajna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Outcastes</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Who among the following composed hymns in the Rigveda?</t>
+          <t>‘Nasadiya Sukta’ in the Rigveda is associated with:</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vyasa</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Valmiki</t>
+          <t>War</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rishis</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Law</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rishis</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Who among the following was a famous female seer (Rishika) in the Rigveda?</t>
+          <t>The term 'Arya' in Vedic texts refers to:</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lopamudra</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Maitreyi</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gargi</t>
+          <t>Cultural group</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Caste</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Cultural group</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The four ‘Ashramas’ in Vedic life refer to:</t>
+          <t>Which term referred to tribal kinship group in Vedic society?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Caste groups</t>
+          <t>Grama</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Life stages</t>
+          <t>Jana</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Religious texts</t>
+          <t>Rashtra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sacrifices</t>
+          <t>Desh</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Life stages</t>
+          <t>Jana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>‘Dasas’ and ‘Dasyus’ referred to:</t>
+          <t>In the Later Vedic period, the power of the king became:</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Less significant</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Enemies</t>
+          <t>Ceremonial</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Craftsmen</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slaves and indigenous people</t>
+          <t>Democratic</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Slaves and indigenous people</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which social institution became prominent during the Later Vedic period?</t>
+          <t>What is the primary source of knowledge about the early Vedic society?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sati</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Caste system</t>
+          <t>Manusmriti</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Joint family</t>
+          <t>Vedas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Temple worship</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Caste system</t>
+          <t>Vedas</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The practice of ‘Sati’ is:</t>
+          <t>The Later Vedic society saw the beginning of:</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mentioned in Rigveda</t>
+          <t>Nomadic culture</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Later development</t>
+          <t>Republics</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prescribed in Upanishads</t>
+          <t>Urbanization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Practiced in Early Vedic period</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Later development</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The term 'Dharma' during Vedic age mainly meant:</t>
+          <t>Who were ‘Nishadas’ as per Vedic references?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Religion</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rituals</t>
+          <t>Enemies</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Moral duty</t>
+          <t>Forest dwellers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Caste law</t>
+          <t>Traders</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Moral duty</t>
+          <t>Forest dwellers</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Upanishads emphasize which philosophical idea?</t>
+          <t>In Vedic rituals, who recited hymns and performed sacrifices?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Shudras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bhakti</t>
+          <t>Vaishyas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yajna</t>
+          <t>Brahmins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Polytheism</t>
+          <t>Rishis</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Brahmins</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>‘Gopati’ in the Vedic period means:</t>
+          <t>The social order in Vedic times was initially based on:</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Village leader</t>
+          <t>Birth</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cow protector</t>
+          <t>Occupation</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>God</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Scholar</t>
+          <t>Property</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cow protector</t>
+          <t>Occupation</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What marked the transition from Early to Later Vedic period?</t>
+          <t>Which goddess is mentioned in Vedic texts as the goddess of speech?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Discovery of fire</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Geographical shift eastwards</t>
+          <t>Durga</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Introduction of Jainism</t>
+          <t>Parvati</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fall of Harappan cities</t>
+          <t>Lakshmi</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Geographical shift eastwards</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The term ‘Yajna’ in the Vedic period refers to:</t>
+          <t>Which stage followed Grihastha in the ashrama system?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Meditation</t>
+          <t>Brahmacharya</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Farming</t>
+          <t>Sannyasa</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sacrifice/ritual</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>War strategy</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sacrifice/ritual</t>
+          <t>Vanaprastha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>‘Varnashrama Dharma’ is a concept developed in which period?</t>
+          <t>What is the subject matter of ‘Nirukta’, one of the Vedangas?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Early Vedic</t>
+          <t>Grammar</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Later Vedic</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Etymology</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buddhist</t>
+          <t>Chanting</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Later Vedic</t>
+          <t>Etymology</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which Veda is considered the oldest?</t>
+          <t>In the Vedic age, 'Sabha' and 'Samiti' were:</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Religious texts</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Festivals</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Tribal assemblies</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Yajnas</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Tribal assemblies</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The 'Purusha Sukta' of the Rigveda describes the origin of:</t>
+          <t>Women in early Vedic society had:</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The Universe</t>
+          <t>No rights</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Castes</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kingship</t>
+          <t>No property rights</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>No religious roles</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Castes</t>
+          <t>Right to education</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>In the Later Vedic period, who performed the ‘Rajasuya’ sacrifice?</t>
+          <t>Which of the following is a later Vedic text?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Traders</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>In the Vedic age, 'Sabha' and 'Samiti' were:</t>
+          <t>Which Vedic deity is associated with thunder and war?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Religious texts</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Festivals</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tribal assemblies</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yajnas</t>
+          <t>Vayu</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tribal assemblies</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What is the subject matter of ‘Nirukta’, one of the Vedangas?</t>
+          <t>Which of the following is considered a Vedanga?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Grammar</t>
+          <t>Brahmana</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Aranyaka</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Etymology</t>
+          <t>Jyotisha</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chanting</t>
+          <t>Upanishad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Etymology</t>
+          <t>Jyotisha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>‘Soma’ was a:</t>
+          <t>The Vedic education system emphasized:</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sacrificial animal</t>
+          <t>Warrior skills</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hallucinogenic drink</t>
+          <t>Practical training</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Spiritual and moral training</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sacred book</t>
+          <t>Political science</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hallucinogenic drink</t>
+          <t>Spiritual and moral training</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which term refers to the priestly scholar in the Vedic age?</t>
+          <t>Which Vedic god was considered the ‘King of Gods’?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rathi</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Purohita</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Senani</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gopa</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Purohita</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Who was responsible for protecting the tribe in Vedic society?</t>
+          <t>The Upanishads emphasize which philosophical idea?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brahmin</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Vaishya</t>
+          <t>Bhakti</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>King (Rajan)</t>
+          <t>Yajna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guru</t>
+          <t>Polytheism</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>King (Rajan)</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Vedic education system emphasized:</t>
+          <t>Which Veda is considered the oldest?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Warrior skills</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Practical training</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spiritual and moral training</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Political science</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Spiritual and moral training</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which Vedic text primarily deals with melodies and chants?</t>
+          <t>Which Vedic deity is associated with the Sun?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Soma</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The education in Vedic times was imparted at:</t>
+          <t>The term ‘Rita’ in Vedic culture refers to:</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Rituals</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Gurukuls</t>
+          <t>Sacrifice</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palaces</t>
+          <t>Cosmic order</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Monasteries</t>
+          <t>Wealth</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gurukuls</t>
+          <t>Cosmic order</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Who compiled the hymns of the Rigveda?</t>
+          <t>Who performed the religious rituals in Vedic times?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vashistha</t>
+          <t>Kshatriyas</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Vyasa</t>
+          <t>Shudras</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atri</t>
+          <t>Brahmins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Patanjali</t>
+          <t>Vaishyas</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Vyasa</t>
+          <t>Brahmins</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>In Vedic rituals, who recited hymns and performed sacrifices?</t>
+          <t>The Vedic economy was primarily:</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Shudras</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Vaishyas</t>
+          <t>Agrarian</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brahmins</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rishis</t>
+          <t>Trade-based</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Brahmins</t>
+          <t>Agrarian</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Who were ‘Nishadas’ as per Vedic references?</t>
+          <t>The decline of the Rigvedic society was marked by:</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>End of tribal assemblies</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Enemies</t>
+          <t>Rise of democratic rule</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Forest dwellers</t>
+          <t>Mass migration</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Traders</t>
+          <t>Urbanization</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Forest dwellers</t>
+          <t>End of tribal assemblies</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Vedic text ‘Shatapatha Brahmana’ is related to which Veda?</t>
+          <t>‘Varnashrama Dharma’ is a concept developed in which period?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Early Vedic</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Later Vedic</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Buddhist</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Later Vedic</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>In Vedic rituals, the 'Ashvamedha' was a:</t>
+          <t>Which Vedic river is frequently mentioned in the Rigveda?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fertility rite</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Horse sacrifice</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rain ceremony</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Funeral</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Horse sacrifice</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which stage of life emphasized forest-dwelling and meditation?</t>
+          <t>The Atharvaveda is primarily associated with:</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Grihastha</t>
+          <t>Sacrifice</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Brahmacharya</t>
+          <t>War</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Medicine and spells</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sannyasa</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Medicine and spells</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which Vedic god is regarded as the sustainer of cosmic and moral order?</t>
+          <t>Which metal was known to the Vedic people?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vayu</t>
+          <t>Alloys</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Who were known as ‘Rajanyas’ in Vedic texts?</t>
+          <t>‘Panis’ in the Rigveda were described as:</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Farmers</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Warrior class</t>
+          <t>Merchants</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Servants</t>
+          <t>Enemies or demons</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Cattle herders</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Warrior class</t>
+          <t>Enemies or demons</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which of the following is a later Vedic text?</t>
+          <t>Which was the language of Vedic literature?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which text elaborates on the performance of Yajnas?</t>
+          <t>The Vedic people primarily lived in which region of India?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Deccan Plateau</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Brahmanas</t>
+          <t>Indo-Gangetic plain</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Punjab and Haryana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Eastern India</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Brahmanas</t>
+          <t>Punjab and Haryana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which Vedic deity is associated with the Sun?</t>
+          <t>Which of the following was not a social class in Vedic society?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Brahmin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Kshatriya</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Sudra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Soma</t>
+          <t>Dalit</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Dalit</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What was the main occupation of the Vedic Aryans?</t>
+          <t>The term 'Grihapati' in the Vedic society referred to:</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Village head</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hunting</t>
+          <t>Head of the family</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Craftsmanship</t>
+          <t>Warrior</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Head of the family</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Vedic people primarily lived in which region of India?</t>
+          <t>The 'Purusha Sukta' of the Rigveda describes the origin of:</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Deccan Plateau</t>
+          <t>The Universe</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Indo-Gangetic plain</t>
+          <t>Castes</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Punjab and Haryana</t>
+          <t>Kingship</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Eastern India</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Punjab and Haryana</t>
+          <t>Castes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The term 'Grihapati' in the Vedic society referred to:</t>
+          <t>Which animal was the most sacred and central to Vedic rituals?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Village head</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Head of the family</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Warrior</t>
+          <t>Goat</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Head of the family</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which Vedic god is considered as the messenger between gods and humans?</t>
+          <t>‘Soma’ was a:</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Sacrificial animal</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Hallucinogenic drink</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Sacred book</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Hallucinogenic drink</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which Vedic river is frequently mentioned in the Rigveda?</t>
+          <t>Who among the following composed hymns in the Rigveda?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Vyasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Valmiki</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Rishis</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Rishis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What is the primary source of knowledge about the early Vedic society?</t>
+          <t>Who among the following was a famous female seer (Rishika) in the Rigveda?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Lopamudra</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Manusmriti</t>
+          <t>Maitreyi</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vedas</t>
+          <t>Gargi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Vedas</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which Vedic text contains the philosophical essence of the Vedas?</t>
+          <t>Who compiled the hymns of the Rigveda?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brahmana</t>
+          <t>Vashistha</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Aranyaka</t>
+          <t>Vyasa</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Atri</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smritis</t>
+          <t>Patanjali</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Vyasa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>‘Panis’ in the Rigveda were described as:</t>
+          <t>What was the role of 'Brahmins' in Vedic society?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Merchants</t>
+          <t>Traders</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Enemies or demons</t>
+          <t>Priests and scholars</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cattle herders</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Enemies or demons</t>
+          <t>Priests and scholars</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The term ‘Nadi’ in Rigveda refers to:</t>
+          <t>Agni in Vedic literature is the god of:</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2070,1102 +2070,1102 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The term ‘Rita’ in Vedic culture refers to:</t>
+          <t>Who was responsible for protecting the tribe in Vedic society?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rituals</t>
+          <t>Brahmin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sacrifice</t>
+          <t>Vaishya</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cosmic order</t>
+          <t>King (Rajan)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wealth</t>
+          <t>Guru</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cosmic order</t>
+          <t>King (Rajan)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The word ‘Aryavarta’ in Vedic literature refers to:</t>
+          <t>‘Brahmacharya’ refers to which stage of life in Vedic philosophy?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Southern India</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Entire Indian subcontinent</t>
+          <t>Retirement</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Land of Aryans</t>
+          <t>Celibate student</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ganges delta</t>
+          <t>Renunciation</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Land of Aryans</t>
+          <t>Celibate student</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which term referred to tribal kinship group in Vedic society?</t>
+          <t>‘Gopati’ in the Vedic period means:</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Grama</t>
+          <t>Village leader</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Jana</t>
+          <t>Cow protector</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rashtra</t>
+          <t>God</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Desh</t>
+          <t>Scholar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Jana</t>
+          <t>Cow protector</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The social order in Vedic times was initially based on:</t>
+          <t>The education in Vedic times was imparted at:</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Birth</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Occupation</t>
+          <t>Gurukuls</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Palaces</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>Monasteries</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Occupation</t>
+          <t>Gurukuls</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which of the following is considered a Vedanga?</t>
+          <t>Who were known as ‘Rajanyas’ in Vedic texts?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brahmana</t>
+          <t>Farmers</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Aranyaka</t>
+          <t>Warrior class</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jyotisha</t>
+          <t>Servants</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Upanishad</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Jyotisha</t>
+          <t>Warrior class</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Who performed the religious rituals in Vedic times?</t>
+          <t>What was the main occupation of the Vedic Aryans?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kshatriyas</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Shudras</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brahmins</t>
+          <t>Hunting</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaishyas</t>
+          <t>Craftsmanship</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Brahmins</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which of the following was not a social class in Vedic society?</t>
+          <t>Which Vedic text contains the philosophical essence of the Vedas?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brahmin</t>
+          <t>Brahmana</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Kshatriya</t>
+          <t>Aranyaka</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sudra</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dalit</t>
+          <t>Smritis</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dalit</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which Vedic god was considered the ‘King of Gods’?</t>
+          <t>Which text elaborates on the performance of Yajnas?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Brahmanas</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Surya</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Brahmanas</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Later Vedic society saw the emergence of:</t>
+          <t>Which social institution became prominent during the Later Vedic period?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tribal democracy</t>
+          <t>Sati</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Slavery</t>
+          <t>Caste system</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Joint family</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Guilds</t>
+          <t>Temple worship</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Caste system</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Vedic economy was primarily:</t>
+          <t>‘Vratyas’ in the Vedic period were:</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Outcastes</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Agrarian</t>
+          <t>Nomadic tribes</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trade-based</t>
+          <t>Scholars</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Agrarian</t>
+          <t>Outcastes</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which metal was known to the Vedic people?</t>
+          <t>In the Later Vedic period, who performed the ‘Rajasuya’ sacrifice?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Traders</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Alloys</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Agni in Vedic literature is the god of:</t>
+          <t>The practice of ‘Sati’ is:</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Mentioned in Rigveda</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Later development</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Prescribed in Upanishads</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Practiced in Early Vedic period</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Later development</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>What was the role of 'Vaishyas' in the Vedic period?</t>
+          <t>Which Vedic god is regarded as the sustainer of cosmic and moral order?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Agriculture and trade</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Slaves</t>
+          <t>Vayu</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Agriculture and trade</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Later Vedic society saw the beginning of:</t>
+          <t>Which Vedic god is considered as the messenger between gods and humans?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nomadic culture</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Republics</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Urbanization</t>
+          <t>Varuna</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Surya</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The decline of the Rigvedic society was marked by:</t>
+          <t>In Vedic rituals, the 'Ashvamedha' was a:</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>End of tribal assemblies</t>
+          <t>Fertility rite</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Rise of democratic rule</t>
+          <t>Horse sacrifice</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mass migration</t>
+          <t>Rain ceremony</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Urbanization</t>
+          <t>Funeral</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>End of tribal assemblies</t>
+          <t>Horse sacrifice</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which Vedic deity is associated with thunder and war?</t>
+          <t>The word ‘Aryavarta’ in Vedic literature refers to:</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Varuna</t>
+          <t>Southern India</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Entire Indian subcontinent</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Land of Aryans</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vayu</t>
+          <t>Ganges delta</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Land of Aryans</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What was the role of 'Brahmins' in Vedic society?</t>
+          <t>What marked the transition from Early to Later Vedic period?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Discovery of fire</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Traders</t>
+          <t>Geographical shift eastwards</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Priests and scholars</t>
+          <t>Introduction of Jainism</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Fall of Harappan cities</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Priests and scholars</t>
+          <t>Geographical shift eastwards</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The term ‘Yupa’ in Vedic rituals refers to:</t>
+          <t>The term ‘Yajna’ in the Vedic period refers to:</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sacred chant</t>
+          <t>Meditation</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sacrifice altar</t>
+          <t>Farming</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pillar for tying the sacrificial animal</t>
+          <t>Sacrifice/ritual</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Priest robe</t>
+          <t>War strategy</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pillar for tying the sacrificial animal</t>
+          <t>Sacrifice/ritual</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>‘Nasadiya Sukta’ in the Rigveda is associated with:</t>
+          <t>The ‘Gayatri Mantra’ is found in which Veda?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cosmology</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cosmology</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which animal was the most sacred and central to Vedic rituals?</t>
+          <t>Which term refers to the priestly scholar in the Vedic age?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Rathi</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Purohita</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Senani</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Goat</t>
+          <t>Gopa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Purohita</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which was the language of Vedic literature?</t>
+          <t>What was the role of 'Vaishyas' in the Vedic period?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Agriculture and trade</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Slaves</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Agriculture and trade</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>In the Later Vedic period, the power of the king became:</t>
+          <t>The term ‘Yupa’ in Vedic rituals refers to:</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Less significant</t>
+          <t>Sacred chant</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ceremonial</t>
+          <t>Sacrifice altar</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>Pillar for tying the sacrificial animal</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Priest robe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>Pillar for tying the sacrificial animal</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Women in early Vedic society had:</t>
+          <t>Which Vedic text primarily deals with melodies and chants?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>No rights</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>No property rights</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>No religious roles</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Right to education</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which goddess is mentioned in Vedic texts as the goddess of speech?</t>
+          <t>The four ‘Ashramas’ in Vedic life refer to:</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Caste groups</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Durga</t>
+          <t>Life stages</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Parvati</t>
+          <t>Religious texts</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lakshmi</t>
+          <t>Sacrifices</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Life stages</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The term 'Arya' in Vedic texts refers to:</t>
+          <t>The term ‘Nadi’ in Rigveda refers to:</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Race</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cultural group</t>
+          <t>River</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Caste</t>
+          <t>Mountain</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cultural group</t>
+          <t>River</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Atharvaveda is primarily associated with:</t>
+          <t>Which god was most important in the Rigvedic period?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sacrifice</t>
+          <t>Shiva</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Medicine and spells</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Brahma</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Medicine and spells</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What was the term used for tax or offering to the king?</t>
+          <t>The Vedic text ‘Shatapatha Brahmana’ is related to which Veda?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dharma</t>
+          <t>Samaveda</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Atharvaveda</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Daan</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Yajna</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Yajurveda</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>‘Brahmacharya’ refers to which stage of life in Vedic philosophy?</t>
+          <t>‘Dasas’ and ‘Dasyus’ referred to:</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Enemies</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Celibate student</t>
+          <t>Craftsmen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Renunciation</t>
+          <t>Slaves and indigenous people</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Celibate student</t>
+          <t>Slaves and indigenous people</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which stage followed Grihastha in the ashrama system?</t>
+          <t>The term 'Dharma' during Vedic age mainly meant:</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brahmacharya</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sannyasa</t>
+          <t>Rituals</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Moral duty</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Caste law</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Vanaprastha</t>
+          <t>Moral duty</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The ‘Gayatri Mantra’ is found in which Veda?</t>
+          <t>The Later Vedic society saw the emergence of:</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Yajurveda</t>
+          <t>Tribal democracy</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Atharvaveda</t>
+          <t>Slavery</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Samaveda</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Guilds</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
